--- a/data/nitaqat.xlsx
+++ b/data/nitaqat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/Localization2/Localization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9B2C10-D856-4E6B-89D8-FF5A13E3DA17}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFCBA3C0-AF54-4D41-9065-0D18AF0720C2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="مواد_البناء_غير سعوديين" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="303">
   <si>
     <t>رقم الإقامة/الهوية</t>
   </si>
@@ -364,12 +364,6 @@
   </si>
   <si>
     <t>أخصائي إداري</t>
-  </si>
-  <si>
-    <t>1121290660</t>
-  </si>
-  <si>
-    <t>هيام سويد بن محمد الباتل</t>
   </si>
   <si>
     <t>مدخل بيانات</t>
@@ -1011,7 +1005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1022,6 +1016,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2030,19 +2030,19 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2093,7 +2093,7 @@
         <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2127,7 +2127,7 @@
         <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2144,7 +2144,7 @@
         <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,41 +2161,41 @@
         <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>287</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>276</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2235,7 +2235,7 @@
         <v>2078731821</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -2244,7 +2244,7 @@
         <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>2580295273</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -2269,7 +2269,7 @@
         <v>2283300677</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -2278,7 +2278,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2286,7 +2286,7 @@
         <v>2530357983</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -2303,7 +2303,7 @@
         <v>2530358106</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -2320,7 +2320,7 @@
         <v>2258976584</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -2337,7 +2337,7 @@
         <v>2605427505</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -2354,7 +2354,7 @@
         <v>2530358569</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
@@ -2363,7 +2363,7 @@
         <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2371,7 +2371,7 @@
         <v>2530358890</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -2388,7 +2388,7 @@
         <v>2533708026</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -2405,7 +2405,7 @@
         <v>2515586051</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
@@ -2422,16 +2422,16 @@
         <v>2560334357</v>
       </c>
       <c r="B13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" t="s">
         <v>146</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2439,7 +2439,7 @@
         <v>2383210875</v>
       </c>
       <c r="B14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -2456,7 +2456,7 @@
         <v>2493040634</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -2473,7 +2473,7 @@
         <v>2493040725</v>
       </c>
       <c r="B16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
@@ -2490,7 +2490,7 @@
         <v>2577540806</v>
       </c>
       <c r="B17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -2507,7 +2507,7 @@
         <v>2577541325</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -2524,7 +2524,7 @@
         <v>2501003012</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -2533,7 +2533,7 @@
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2541,7 +2541,7 @@
         <v>2276275266</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -2550,7 +2550,7 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2558,7 +2558,7 @@
         <v>2518963695</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -2575,7 +2575,7 @@
         <v>2518963729</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
@@ -2592,7 +2592,7 @@
         <v>2518963752</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
@@ -2609,7 +2609,7 @@
         <v>2035432513</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
@@ -2618,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2626,13 +2626,13 @@
         <v>2615046204</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -2643,13 +2643,13 @@
         <v>2615046394</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
         <v>24</v>
@@ -2660,13 +2660,13 @@
         <v>2615670151</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
@@ -2677,13 +2677,13 @@
         <v>2615670292</v>
       </c>
       <c r="B28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
@@ -2694,7 +2694,7 @@
         <v>2512170099</v>
       </c>
       <c r="B29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -2711,7 +2711,7 @@
         <v>2607303431</v>
       </c>
       <c r="B30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
@@ -2728,7 +2728,7 @@
         <v>2624799421</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -2745,7 +2745,7 @@
         <v>2493899930</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
@@ -2762,13 +2762,13 @@
         <v>2453564094</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
         <v>37</v>
@@ -2779,7 +2779,7 @@
         <v>2337203240</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -2788,7 +2788,7 @@
         <v>62</v>
       </c>
       <c r="E34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2796,7 +2796,7 @@
         <v>2525753071</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
@@ -2813,7 +2813,7 @@
         <v>2230186922</v>
       </c>
       <c r="B36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -2830,7 +2830,7 @@
         <v>2393976135</v>
       </c>
       <c r="B37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -2847,7 +2847,7 @@
         <v>2473013759</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
@@ -2856,7 +2856,7 @@
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2864,7 +2864,7 @@
         <v>2595214913</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -2881,7 +2881,7 @@
         <v>2595216363</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
@@ -2898,7 +2898,7 @@
         <v>2636721876</v>
       </c>
       <c r="B41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
@@ -2915,7 +2915,7 @@
         <v>2636722643</v>
       </c>
       <c r="B42" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
@@ -2932,7 +2932,7 @@
         <v>2504976644</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
         <v>7</v>
@@ -2949,7 +2949,7 @@
         <v>2603405008</v>
       </c>
       <c r="B44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C44" t="s">
         <v>7</v>
@@ -2958,7 +2958,7 @@
         <v>33</v>
       </c>
       <c r="E44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -2966,7 +2966,7 @@
         <v>2394567073</v>
       </c>
       <c r="B45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
@@ -2983,7 +2983,7 @@
         <v>2564182638</v>
       </c>
       <c r="B46" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
@@ -2992,7 +2992,7 @@
         <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3000,7 +3000,7 @@
         <v>2487396620</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
@@ -3009,7 +3009,7 @@
         <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3017,7 +3017,7 @@
         <v>2367348733</v>
       </c>
       <c r="B48" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
@@ -3034,7 +3034,7 @@
         <v>2531762959</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
@@ -3043,7 +3043,7 @@
         <v>40</v>
       </c>
       <c r="E49" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3051,16 +3051,16 @@
         <v>2529279966</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
       </c>
       <c r="D50" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E50" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3068,7 +3068,7 @@
         <v>2596038139</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
@@ -3085,7 +3085,7 @@
         <v>2515789507</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
@@ -3102,7 +3102,7 @@
         <v>2506215892</v>
       </c>
       <c r="B53" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
@@ -3119,7 +3119,7 @@
         <v>2516179443</v>
       </c>
       <c r="B54" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
@@ -3136,7 +3136,7 @@
         <v>2588542577</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
@@ -3153,7 +3153,7 @@
         <v>2605734991</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
@@ -3170,7 +3170,7 @@
         <v>2605735295</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C57" t="s">
         <v>7</v>
@@ -3187,7 +3187,7 @@
         <v>2530358684</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C58" t="s">
         <v>7</v>
@@ -3196,7 +3196,7 @@
         <v>33</v>
       </c>
       <c r="E58" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3204,7 +3204,7 @@
         <v>2554866240</v>
       </c>
       <c r="B59" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
@@ -3221,7 +3221,7 @@
         <v>2554866331</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C60" t="s">
         <v>7</v>
@@ -3238,7 +3238,7 @@
         <v>2589363452</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C61" t="s">
         <v>7</v>
@@ -3255,7 +3255,7 @@
         <v>2589363882</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
         <v>7</v>
@@ -3272,7 +3272,7 @@
         <v>2589764063</v>
       </c>
       <c r="B63" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
@@ -3289,7 +3289,7 @@
         <v>2430112090</v>
       </c>
       <c r="B64" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
@@ -3306,16 +3306,16 @@
         <v>2529156974</v>
       </c>
       <c r="B65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" t="s">
         <v>210</v>
-      </c>
-      <c r="C65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" t="s">
-        <v>211</v>
-      </c>
-      <c r="E65" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3323,7 +3323,7 @@
         <v>2463896361</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C66" t="s">
         <v>7</v>
@@ -3340,7 +3340,7 @@
         <v>2497835393</v>
       </c>
       <c r="B67" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C67" t="s">
         <v>7</v>
@@ -3357,16 +3357,16 @@
         <v>2484116898</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C68" t="s">
         <v>7</v>
       </c>
       <c r="D68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E68" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3374,7 +3374,7 @@
         <v>2516834427</v>
       </c>
       <c r="B69" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
@@ -3383,7 +3383,7 @@
         <v>27</v>
       </c>
       <c r="E69" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3391,7 +3391,7 @@
         <v>2576410837</v>
       </c>
       <c r="B70" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C70" t="s">
         <v>7</v>
@@ -3408,16 +3408,16 @@
         <v>2560294718</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C71" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D71" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E71" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3425,7 +3425,7 @@
         <v>2512170040</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72" t="s">
         <v>7</v>
@@ -3442,16 +3442,16 @@
         <v>2497213237</v>
       </c>
       <c r="B73" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C73" t="s">
         <v>7</v>
       </c>
       <c r="D73" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E73" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3459,7 +3459,7 @@
         <v>2351101494</v>
       </c>
       <c r="B74" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
@@ -3468,7 +3468,7 @@
         <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -3476,7 +3476,7 @@
         <v>2512170339</v>
       </c>
       <c r="B75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
         <v>7</v>
@@ -3493,7 +3493,7 @@
         <v>2600084855</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C76" t="s">
         <v>7</v>
@@ -3510,7 +3510,7 @@
         <v>2501606293</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C77" t="s">
         <v>7</v>
@@ -3527,7 +3527,7 @@
         <v>2600085118</v>
       </c>
       <c r="B78" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C78" t="s">
         <v>7</v>
@@ -3544,7 +3544,7 @@
         <v>2586004851</v>
       </c>
       <c r="B79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C79" t="s">
         <v>7</v>
@@ -3561,7 +3561,7 @@
         <v>2286419748</v>
       </c>
       <c r="B80" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C80" t="s">
         <v>7</v>
@@ -3570,7 +3570,7 @@
         <v>8</v>
       </c>
       <c r="E80" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3578,16 +3578,16 @@
         <v>2564182158</v>
       </c>
       <c r="B81" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C81" t="s">
         <v>7</v>
       </c>
       <c r="D81" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E81" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3595,7 +3595,7 @@
         <v>2578419893</v>
       </c>
       <c r="B82" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C82" t="s">
         <v>7</v>
@@ -3612,7 +3612,7 @@
         <v>2159616958</v>
       </c>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C83" t="s">
         <v>7</v>
@@ -3629,7 +3629,7 @@
         <v>2183902606</v>
       </c>
       <c r="B84" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C84" t="s">
         <v>7</v>
@@ -3646,7 +3646,7 @@
         <v>2404319457</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C85" t="s">
         <v>7</v>
@@ -3663,7 +3663,7 @@
         <v>2634817239</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C86" t="s">
         <v>7</v>
@@ -3680,7 +3680,7 @@
         <v>2634892166</v>
       </c>
       <c r="B87" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C87" t="s">
         <v>7</v>
@@ -3697,7 +3697,7 @@
         <v>2634892364</v>
       </c>
       <c r="B88" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
         <v>7</v>
@@ -3714,7 +3714,7 @@
         <v>2634892455</v>
       </c>
       <c r="B89" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C89" t="s">
         <v>7</v>
@@ -3731,7 +3731,7 @@
         <v>2513627535</v>
       </c>
       <c r="B90" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C90" t="s">
         <v>7</v>
@@ -3740,7 +3740,7 @@
         <v>62</v>
       </c>
       <c r="E90" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3748,7 +3748,7 @@
         <v>2506045794</v>
       </c>
       <c r="B91" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C91" t="s">
         <v>7</v>
@@ -3765,7 +3765,7 @@
         <v>2398491239</v>
       </c>
       <c r="B92" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C92" t="s">
         <v>7</v>
@@ -3782,7 +3782,7 @@
         <v>2201429236</v>
       </c>
       <c r="B93" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C93" t="s">
         <v>7</v>
@@ -3799,7 +3799,7 @@
         <v>2069513766</v>
       </c>
       <c r="B94" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C94" t="s">
         <v>7</v>
@@ -3808,7 +3808,7 @@
         <v>33</v>
       </c>
       <c r="E94" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3816,7 +3816,7 @@
         <v>2550266494</v>
       </c>
       <c r="B95" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C95" t="s">
         <v>7</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E95" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
         <v>2550269597</v>
       </c>
       <c r="B96" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C96" t="s">
         <v>7</v>
@@ -3855,399 +3855,402 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26" style="3" customWidth="1"/>
-    <col min="3" max="5" width="18" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18" style="6" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="6" customWidth="1"/>
+    <col min="5" max="5" width="21" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="6">
         <v>1124109511</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>1089453607</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>1110133681</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1089453607</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E4" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>1105627804</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E5" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>1084019023</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>1106547050</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>1121112013</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>1106949041</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1110133681</v>
-      </c>
-      <c r="B4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>1112469950</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1105627804</v>
-      </c>
-      <c r="B5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E10" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>1136475348</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1084019023</v>
-      </c>
-      <c r="B6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E11" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>1114963471</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>1106547050</v>
-      </c>
-      <c r="B7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E12" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>1105369316</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1121112013</v>
-      </c>
-      <c r="B8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E13" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>1096980741</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1106949041</v>
-      </c>
-      <c r="B9" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E14" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>1073583906</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E15" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1112469950</v>
-      </c>
-      <c r="B10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" t="s">
-        <v>219</v>
-      </c>
-      <c r="D10" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>1121112096</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1136475348</v>
-      </c>
-      <c r="B11" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E16" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>1124570761</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1114963471</v>
-      </c>
-      <c r="B12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C12" t="s">
-        <v>219</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E17" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>1041509652</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E12" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1105369316</v>
-      </c>
-      <c r="B13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E18" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>1119810917</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>1096980741</v>
-      </c>
-      <c r="B14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E19" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>1109061356</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E14" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>1073583906</v>
-      </c>
-      <c r="B15" t="s">
-        <v>266</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E20" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>1100881737</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>1121112096</v>
-      </c>
-      <c r="B16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C16" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E21" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>1125682029</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>1124570761</v>
-      </c>
-      <c r="B17" t="s">
-        <v>268</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>1041509652</v>
-      </c>
-      <c r="B18" t="s">
-        <v>269</v>
-      </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>1119810917</v>
-      </c>
-      <c r="B19" t="s">
-        <v>271</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>1109061356</v>
-      </c>
-      <c r="B20" t="s">
-        <v>273</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>1100881737</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="E22" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>1145462238</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>1125682029</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>1145462238</v>
-      </c>
-      <c r="B23" t="s">
-        <v>277</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" t="s">
-        <v>278</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4285,10 +4288,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -4302,10 +4305,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -4319,27 +4322,27 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -4348,7 +4351,7 @@
         <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -4358,7 +4361,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="3" customWidth="1"/>
@@ -4381,23 +4384,6 @@
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4420,30 +4406,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -4455,119 +4441,119 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/data/nitaqat.xlsx
+++ b/data/nitaqat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/Localization2/Localization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFCBA3C0-AF54-4D41-9065-0D18AF0720C2}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6FDC06D-2DCB-4A96-942A-5981D9DBE6B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="مواد_البناء_غير سعوديين" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="304">
   <si>
     <t>رقم الإقامة/الهوية</t>
   </si>
@@ -940,6 +940,9 @@
   </si>
   <si>
     <t>هائل لصيانة السيارات</t>
+  </si>
+  <si>
+    <t>عقيل الطيار</t>
   </si>
 </sst>
 </file>
@@ -3852,7 +3855,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="6" customWidth="1"/>
@@ -4252,6 +4255,23 @@
       </c>
       <c r="E23" s="6" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>1111111111</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/data/nitaqat.xlsx
+++ b/data/nitaqat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/Localization2/Localization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6FDC06D-2DCB-4A96-942A-5981D9DBE6B2}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D986E35-C43A-47BD-974A-2BC4F341F730}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="مواد_البناء_غير سعوديين" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="302">
   <si>
     <t>رقم الإقامة/الهوية</t>
   </si>
@@ -808,12 +808,6 @@
   </si>
   <si>
     <t>هشام عبدالله بن دخيل الفهيد</t>
-  </si>
-  <si>
-    <t>أمجاد عايش زايد العنزي</t>
-  </si>
-  <si>
-    <t>أخصائي خدمة عملاء</t>
   </si>
   <si>
     <t>باسل عبدالرزاق عبدالله القشعمي</t>
@@ -2186,16 +2180,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E18" t="s">
         <v>110</v>
@@ -3855,7 +3849,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="6" customWidth="1"/>
@@ -4055,27 +4049,27 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>1114963471</v>
+        <v>1105369316</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>259</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>93</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>260</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>1105369316</v>
+        <v>1096980741</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>7</v>
@@ -4084,12 +4078,12 @@
         <v>93</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>104</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>1096980741</v>
+        <v>1073583906</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>262</v>
@@ -4101,49 +4095,49 @@
         <v>93</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>263</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>1073583906</v>
+        <v>1121112096</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>7</v>
+        <v>217</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>93</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>1121112096</v>
+        <v>1124570761</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>217</v>
+        <v>7</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>93</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>1124570761</v>
+        <v>1041509652</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>7</v>
@@ -4152,12 +4146,12 @@
         <v>93</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>155</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>1041509652</v>
+        <v>1119810917</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>267</v>
@@ -4174,7 +4168,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>1119810917</v>
+        <v>1109061356</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>269</v>
@@ -4191,7 +4185,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>1109061356</v>
+        <v>1100881737</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>271</v>
@@ -4203,15 +4197,15 @@
         <v>93</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>272</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>1100881737</v>
+        <v>1125682029</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>7</v>
@@ -4225,52 +4219,35 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>1125682029</v>
+        <v>1145462238</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>1145462238</v>
+        <v>1111111111</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>276</v>
+        <v>93</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>1111111111</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="6" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4308,10 +4285,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -4325,10 +4302,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -4342,10 +4319,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
         <v>217</v>
@@ -4359,10 +4336,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -4371,7 +4348,7 @@
         <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -4426,30 +4403,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -4461,119 +4438,119 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B14" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/data/nitaqat.xlsx
+++ b/data/nitaqat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3113719057d24bf/Desktop/Localization2/Localization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D986E35-C43A-47BD-974A-2BC4F341F730}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_F3615385140EEACF356911CEE18786AE072217E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0B04681-43E3-4BC9-9B98-CAAA69C9B77E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="301">
   <si>
     <t>رقم الإقامة/الهوية</t>
   </si>
@@ -934,9 +934,6 @@
   </si>
   <si>
     <t>هائل لصيانة السيارات</t>
-  </si>
-  <si>
-    <t>عقيل الطيار</t>
   </si>
 </sst>
 </file>
@@ -3849,7 +3846,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="6" customWidth="1"/>
@@ -4232,23 +4229,6 @@
       </c>
       <c r="E22" s="6" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>1111111111</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
